--- a/output/pdf_financials_xlsx/EWK.xlsx
+++ b/output/pdf_financials_xlsx/EWK.xlsx
@@ -1275,37 +1275,37 @@
         <v>0.09787800000000001</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>1.841181</v>
@@ -1375,7 +1375,7 @@
         <v>0.012583</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.694698</v>
       </c>
     </row>
     <row r="18">
@@ -1575,37 +1575,37 @@
         <v>0.09787800000000001</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>1.841181</v>
@@ -1614,10 +1614,10 @@
         <v>2.268482</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>15.122285</v>
+        <v>-15.122285</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2.847349</v>
+        <v>-2.847349</v>
       </c>
     </row>
     <row r="21">
@@ -1749,37 +1749,37 @@
         <v>0.09787800000000001</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>1.841181</v>
@@ -1788,10 +1788,10 @@
         <v>2.268482</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>15.122285</v>
+        <v>-15.122285</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>2.847349</v>
+        <v>-2.847349</v>
       </c>
     </row>
     <row r="24">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25.401033</v>
+        <v>-25.401033</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>22.8386</v>
+        <v>-22.8386</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>26.71833</v>
+        <v>-26.71833</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>36.411967</v>
+        <v>-36.411967</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>37.45155</v>
+        <v>-37.45155</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>52.006533</v>
+        <v>-52.006533</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>57.50985</v>
+        <v>-57.50985</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
         <v>113.4241</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-108.016321</v>
+        <v>108.016321</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-142.36745</v>
+        <v>142.36745</v>
       </c>
     </row>
     <row r="27">
@@ -2005,37 +2005,37 @@
         <v>0.09787800000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>1.841181</v>
@@ -2121,37 +2121,37 @@
         <v>0.09787800000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>1.841181</v>
@@ -2271,37 +2271,37 @@
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         <v>0.08313914597735507</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -5998,25 +5998,25 @@
         <v>2.460614</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>2.460614</v>
+        <v>2.905038</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.072637</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.287307</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.107441</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.325441</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.628441</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.796441</v>
       </c>
     </row>
     <row r="93">
@@ -6419,7 +6419,7 @@
         <v>-0.749031</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-1.560196</v>
@@ -10499,7 +10499,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -12213,7 +12217,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -42669,10 +42677,10 @@
         </is>
       </c>
       <c r="T345" s="5" t="n">
-        <v>15.122285</v>
+        <v>-15.122285</v>
       </c>
       <c r="U345" s="5" t="n">
-        <v>2.847349</v>
+        <v>-2.847349</v>
       </c>
     </row>
     <row r="346">
@@ -42871,10 +42879,10 @@
         </is>
       </c>
       <c r="T347" s="5" t="n">
-        <v>15.0073</v>
+        <v>-15.0073</v>
       </c>
       <c r="U347" s="5" t="n">
-        <v>2.834159</v>
+        <v>-2.834159</v>
       </c>
     </row>
     <row r="348">
@@ -46345,16 +46353,16 @@
         </is>
       </c>
       <c r="I384" s="5" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="J384" s="5" t="n">
-        <v>0.214278</v>
+        <v>-0.214278</v>
       </c>
       <c r="K384" s="5" t="n">
-        <v>1.092359</v>
+        <v>-1.092359</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>0.749031</v>
+        <v>-0.749031</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -46362,19 +46370,19 @@
         </is>
       </c>
       <c r="N384" s="5" t="n">
-        <v>1.560196</v>
+        <v>-1.560196</v>
       </c>
       <c r="O384" s="5" t="n">
-        <v>1.150197</v>
+        <v>-1.150197</v>
       </c>
       <c r="P384" s="5" t="n">
-        <v>0.936425</v>
+        <v>-0.936425</v>
       </c>
       <c r="Q384" s="5" t="n">
-        <v>1.045875</v>
+        <v>-1.045875</v>
       </c>
       <c r="R384" s="5" t="n">
-        <v>1.841181</v>
+        <v>-1.841181</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
@@ -46573,10 +46581,10 @@
         </is>
       </c>
       <c r="Q386" s="5" t="n">
-        <v>1.094433</v>
+        <v>-1.094433</v>
       </c>
       <c r="R386" s="5" t="n">
-        <v>1.651944</v>
+        <v>-1.651944</v>
       </c>
       <c r="S386" t="inlineStr">
         <is>
@@ -47326,13 +47334,13 @@
         </is>
       </c>
       <c r="N394" s="5" t="n">
-        <v>1.729323</v>
+        <v>-1.729323</v>
       </c>
       <c r="O394" s="5" t="n">
-        <v>1.039029</v>
+        <v>-1.039029</v>
       </c>
       <c r="P394" s="5" t="n">
-        <v>0.944096</v>
+        <v>-0.944096</v>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
@@ -49622,10 +49630,10 @@
         </is>
       </c>
       <c r="M417" s="5" t="n">
-        <v>0.09063499999999999</v>
+        <v>-0.09063499999999999</v>
       </c>
       <c r="N417" s="5" t="n">
-        <v>0.746645</v>
+        <v>-0.746645</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
@@ -50395,19 +50403,19 @@
         </is>
       </c>
       <c r="H425" s="5" t="n">
-        <v>1.086063</v>
+        <v>-1.086063</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>2.766423</v>
+        <v>-2.766423</v>
       </c>
       <c r="J425" s="5" t="n">
-        <v>0.050695</v>
+        <v>-0.050695</v>
       </c>
       <c r="K425" s="5" t="n">
-        <v>0.853387</v>
+        <v>-0.853387</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>0.284963</v>
+        <v>-0.284963</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -52153,10 +52161,10 @@
         </is>
       </c>
       <c r="H443" s="5" t="n">
-        <v>1.14193</v>
+        <v>-1.14193</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>2.671833</v>
+        <v>-2.671833</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
@@ -52651,10 +52659,10 @@
         </is>
       </c>
       <c r="G448" s="5" t="n">
-        <v>0.762031</v>
+        <v>-0.762031</v>
       </c>
       <c r="H448" s="5" t="n">
-        <v>1.290916</v>
+        <v>-1.290916</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EWK.xlsx
+++ b/output/pdf_financials_xlsx/EWK.xlsx
@@ -2422,55 +2422,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.137212</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.253131</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.37641</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.258815</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.08178000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002165</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.052998</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.046092</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.086924</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.953839</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.090779</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007524</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.288086</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.209206</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.908872</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.016543</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.05399</v>
       </c>
     </row>
     <row r="35">
@@ -2538,55 +2538,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.137212</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.253131</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.37641</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.258815</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.08178000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002165</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.052998</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.046092</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.086924</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.953839</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.090779</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.007524</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.288086</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.209206</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.908872</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.016543</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.05399</v>
       </c>
     </row>
     <row r="37">
@@ -3234,55 +3234,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.159448</v>
+        <v>0.022236</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.270274</v>
+        <v>0.017143</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.400945</v>
+        <v>0.024535</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.27985</v>
+        <v>0.021035</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.109319</v>
+        <v>0.027539</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.011228</v>
+        <v>0.009063</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.05712</v>
+        <v>0.004122</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.049903</v>
+        <v>0.003811</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.09416099999999999</v>
+        <v>0.007237</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.960516</v>
+        <v>0.006677</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.106076</v>
+        <v>0.015297</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.023403</v>
+        <v>0.015879</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.417012</v>
+        <v>0.128926</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.248838</v>
+        <v>0.039632</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.089629</v>
+        <v>0.180757</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.016827</v>
+        <v>0.000284</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.152626</v>
+        <v>0.098636</v>
       </c>
     </row>
     <row r="49">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
